--- a/data/baidu/china_western.xlsx
+++ b/data/baidu/china_western.xlsx
@@ -583,16 +583,24 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>让子弹飞</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>让子弹飞</t>
+        </is>
+      </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
@@ -657,24 +665,30 @@
           <t>https://movie.douban.com/subject/3804891/</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>33283.85714285714</v>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>无人区</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>无人区</t>
+        </is>
+      </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -737,16 +751,24 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>和平饭店</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>和平饭店</t>
+        </is>
+      </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
@@ -814,16 +836,24 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>富贵列车</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>富贵列车</t>
+        </is>
+      </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
@@ -891,16 +921,24 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>黄飞鸿之西域雄狮</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>黄飞鸿之西域雄狮</t>
+        </is>
+      </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
@@ -968,16 +1006,24 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2258068266, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>殖民者</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>殖民者</t>
+        </is>
+      </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
@@ -1045,16 +1091,24 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>上海正午</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>上海正午</t>
+        </is>
+      </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
@@ -1122,16 +1176,24 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>西风烈</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>西风烈</t>
+        </is>
+      </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
@@ -1199,16 +1261,24 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2258286498, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>远去的牧歌</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>远去的牧歌</t>
+        </is>
+      </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
@@ -1276,16 +1346,24 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>决战刹马镇</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>决战刹马镇</t>
+        </is>
+      </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
@@ -1350,24 +1428,30 @@
           <t>https://movie.douban.com/subject/10508901/</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>17172.42857142857</v>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>匹夫</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>匹夫</t>
+        </is>
+      </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1430,16 +1514,24 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>沉默的冰山</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>沉默的冰山</t>
+        </is>
+      </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
@@ -1504,21 +1596,27 @@
           <t>https://movie.douban.com/subject/30234426/</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>来者何人</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>来者何人</t>
+        </is>
+      </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1581,24 +1679,30 @@
           <t>https://movie.douban.com/subject/27063332/</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>700.8571428571429</v>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>金珠玛米</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>金珠玛米</t>
+        </is>
+      </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -1658,21 +1762,27 @@
           <t>https://movie.douban.com/subject/35027217/</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>出门在外</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>出门在外</t>
+        </is>
+      </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1738,16 +1848,24 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2259477546, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>唐人街1871</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>唐人街1871</t>
+        </is>
+      </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
